--- a/code/data/combined/cmb+pelg-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+pelg-w0wacdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38828223.96634194</v>
+        <v>44039754.06063955</v>
       </c>
       <c r="C2" t="n">
-        <v>-133606560.1691612</v>
+        <v>-148005237.0489501</v>
       </c>
       <c r="D2" t="n">
-        <v>40456438.32383012</v>
+        <v>46500797.20826009</v>
       </c>
       <c r="E2" t="n">
-        <v>-530213.2285107054</v>
+        <v>-588057.4178194727</v>
       </c>
       <c r="F2" t="n">
-        <v>-1346163.24048146</v>
+        <v>-1348920.817637979</v>
       </c>
       <c r="G2" t="n">
-        <v>898216.1462240216</v>
+        <v>1066599.76698259</v>
       </c>
       <c r="H2" t="n">
-        <v>-2574861.584729737</v>
+        <v>-2930517.236145429</v>
       </c>
       <c r="I2" t="n">
-        <v>6334393.911892149</v>
+        <v>7254977.249014789</v>
       </c>
       <c r="J2" t="n">
-        <v>1708859.468096137</v>
+        <v>1958068.581744205</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-133606560.1769436</v>
+        <v>-148005237.0566424</v>
       </c>
       <c r="C3" t="n">
-        <v>885673649.157617</v>
+        <v>893465499.2868516</v>
       </c>
       <c r="D3" t="n">
-        <v>-88909611.7778005</v>
+        <v>-111344024.7872749</v>
       </c>
       <c r="E3" t="n">
-        <v>16001954.04936039</v>
+        <v>16605025.97891812</v>
       </c>
       <c r="F3" t="n">
-        <v>6683521.901744495</v>
+        <v>6636531.792174394</v>
       </c>
       <c r="G3" t="n">
-        <v>-3868534.013015492</v>
+        <v>-4472591.681449256</v>
       </c>
       <c r="H3" t="n">
-        <v>7937156.825938717</v>
+        <v>8965870.945704388</v>
       </c>
       <c r="I3" t="n">
-        <v>-24745860.92139443</v>
+        <v>-27617039.3796506</v>
       </c>
       <c r="J3" t="n">
-        <v>-6673793.298951881</v>
+        <v>-7452963.89540746</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40456438.32283317</v>
+        <v>46500797.20749153</v>
       </c>
       <c r="C4" t="n">
-        <v>-88909611.76583526</v>
+        <v>-111344024.7763549</v>
       </c>
       <c r="D4" t="n">
-        <v>48791138.15359164</v>
+        <v>54893365.23520559</v>
       </c>
       <c r="E4" t="n">
-        <v>880435.7660483969</v>
+        <v>793229.8339020922</v>
       </c>
       <c r="F4" t="n">
-        <v>-889123.3338586149</v>
+        <v>-913245.4730555015</v>
       </c>
       <c r="G4" t="n">
-        <v>975967.5484906967</v>
+        <v>1157336.032151716</v>
       </c>
       <c r="H4" t="n">
-        <v>-2832694.826619963</v>
+        <v>-3234671.32902831</v>
       </c>
       <c r="I4" t="n">
-        <v>6518444.03133075</v>
+        <v>7559822.774260156</v>
       </c>
       <c r="J4" t="n">
-        <v>1761616.477019866</v>
+        <v>2043262.529416209</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-530213.2287338275</v>
+        <v>-588057.4181561287</v>
       </c>
       <c r="C5" t="n">
-        <v>16001954.04988084</v>
+        <v>16605025.97989361</v>
       </c>
       <c r="D5" t="n">
-        <v>880435.7657695215</v>
+        <v>793229.8335153393</v>
       </c>
       <c r="E5" t="n">
-        <v>935381.2570571379</v>
+        <v>1022606.011761798</v>
       </c>
       <c r="F5" t="n">
-        <v>44400.76214397347</v>
+        <v>63279.24836812064</v>
       </c>
       <c r="G5" t="n">
-        <v>-68216.51065880559</v>
+        <v>-75772.40204461841</v>
       </c>
       <c r="H5" t="n">
-        <v>-2808.141818762649</v>
+        <v>-2041.389946148849</v>
       </c>
       <c r="I5" t="n">
-        <v>-265198.3580132492</v>
+        <v>-295595.2829141963</v>
       </c>
       <c r="J5" t="n">
-        <v>-71576.56462969942</v>
+        <v>-79834.20817330413</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1346163.240547124</v>
+        <v>-1348920.817667929</v>
       </c>
       <c r="C6" t="n">
-        <v>6683521.902062046</v>
+        <v>6636531.792355914</v>
       </c>
       <c r="D6" t="n">
-        <v>-889123.3339208657</v>
+        <v>-913245.4730797858</v>
       </c>
       <c r="E6" t="n">
-        <v>44400.76214958642</v>
+        <v>63279.24837192587</v>
       </c>
       <c r="F6" t="n">
-        <v>581419.2640443039</v>
+        <v>582396.8324677978</v>
       </c>
       <c r="G6" t="n">
-        <v>101143.0818905515</v>
+        <v>99925.90871882709</v>
       </c>
       <c r="H6" t="n">
-        <v>41673.44401834789</v>
+        <v>40774.07318896861</v>
       </c>
       <c r="I6" t="n">
-        <v>-10854.17053677102</v>
+        <v>-14735.8937587831</v>
       </c>
       <c r="J6" t="n">
-        <v>-1254.66068346315</v>
+        <v>-2293.512771024609</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>898216.1462235694</v>
+        <v>1066599.767014834</v>
       </c>
       <c r="C7" t="n">
-        <v>-3868534.012705125</v>
+        <v>-4472591.681269914</v>
       </c>
       <c r="D7" t="n">
-        <v>975967.5485294439</v>
+        <v>1157336.032215955</v>
       </c>
       <c r="E7" t="n">
-        <v>-68216.51064971763</v>
+        <v>-75772.40203283144</v>
       </c>
       <c r="F7" t="n">
-        <v>101143.081893343</v>
+        <v>99925.90872018988</v>
       </c>
       <c r="G7" t="n">
-        <v>65777.78316208544</v>
+        <v>71677.9097425751</v>
       </c>
       <c r="H7" t="n">
-        <v>-71510.95841610139</v>
+        <v>-82724.82226459144</v>
       </c>
       <c r="I7" t="n">
-        <v>228053.0394103628</v>
+        <v>259398.9110597585</v>
       </c>
       <c r="J7" t="n">
-        <v>62383.74497446581</v>
+        <v>70873.40035314878</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2574861.5847087</v>
+        <v>-2930517.236132021</v>
       </c>
       <c r="C8" t="n">
-        <v>7937156.825311095</v>
+        <v>8965870.945115587</v>
       </c>
       <c r="D8" t="n">
-        <v>-2832694.826667829</v>
+        <v>-3234671.32906802</v>
       </c>
       <c r="E8" t="n">
-        <v>-2808.141835454359</v>
+        <v>-2041.38997022906</v>
       </c>
       <c r="F8" t="n">
-        <v>41673.44401386567</v>
+        <v>40774.07318700408</v>
       </c>
       <c r="G8" t="n">
-        <v>-71510.95841529478</v>
+        <v>-82724.82226181155</v>
       </c>
       <c r="H8" t="n">
-        <v>178347.6486148892</v>
+        <v>202682.2811658795</v>
       </c>
       <c r="I8" t="n">
-        <v>-437277.5292673233</v>
+        <v>-499249.1349861964</v>
       </c>
       <c r="J8" t="n">
-        <v>-118213.0328328019</v>
+        <v>-134984.6682923818</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6334393.911915407</v>
+        <v>7254977.249111942</v>
       </c>
       <c r="C9" t="n">
-        <v>-24745860.91996929</v>
+        <v>-27617039.37853128</v>
       </c>
       <c r="D9" t="n">
-        <v>6518444.031548794</v>
+        <v>7559822.774511473</v>
       </c>
       <c r="E9" t="n">
-        <v>-265198.3579704585</v>
+        <v>-295595.2828532541</v>
       </c>
       <c r="F9" t="n">
-        <v>-10854.17052329971</v>
+        <v>-14735.89375235676</v>
       </c>
       <c r="G9" t="n">
-        <v>228053.0394114197</v>
+        <v>259398.9110573159</v>
       </c>
       <c r="H9" t="n">
-        <v>-437277.5292730745</v>
+        <v>-499249.1349955797</v>
       </c>
       <c r="I9" t="n">
-        <v>1192572.943902745</v>
+        <v>1360674.733508436</v>
       </c>
       <c r="J9" t="n">
-        <v>323118.8342509508</v>
+        <v>368633.3830704075</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1708859.468102109</v>
+        <v>1958068.581770845</v>
       </c>
       <c r="C10" t="n">
-        <v>-6673793.298563515</v>
+        <v>-7452963.895106772</v>
       </c>
       <c r="D10" t="n">
-        <v>1761616.477078725</v>
+        <v>2043262.529484396</v>
       </c>
       <c r="E10" t="n">
-        <v>-71576.56461807994</v>
+        <v>-79834.20815671573</v>
       </c>
       <c r="F10" t="n">
-        <v>-1254.660679806908</v>
+        <v>-2293.512769282442</v>
       </c>
       <c r="G10" t="n">
-        <v>62383.7449747395</v>
+        <v>70873.40035249558</v>
       </c>
       <c r="H10" t="n">
-        <v>-118213.0328343391</v>
+        <v>-134984.6682949461</v>
       </c>
       <c r="I10" t="n">
-        <v>323118.8342508848</v>
+        <v>368633.3830704574</v>
       </c>
       <c r="J10" t="n">
-        <v>87613.88608874669</v>
+        <v>99937.28304164347</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg-w0wacdm-free.xlsx
+++ b/code/data/combined/cmb+pelg-w0wacdm-free.xlsx
@@ -482,31 +482,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44039754.06063955</v>
+        <v>43189604.82235527</v>
       </c>
       <c r="C2" t="n">
-        <v>-148005237.0489501</v>
+        <v>-145165973.5468991</v>
       </c>
       <c r="D2" t="n">
-        <v>46500797.20826009</v>
+        <v>45581849.69548564</v>
       </c>
       <c r="E2" t="n">
-        <v>-588057.4178194727</v>
+        <v>-580802.6110220458</v>
       </c>
       <c r="F2" t="n">
-        <v>-1348920.817637979</v>
+        <v>-1341304.424110554</v>
       </c>
       <c r="G2" t="n">
-        <v>1066599.76698259</v>
+        <v>1039709.187982573</v>
       </c>
       <c r="H2" t="n">
-        <v>-2930517.236145429</v>
+        <v>-2870677.146711545</v>
       </c>
       <c r="I2" t="n">
-        <v>7254977.249014789</v>
+        <v>7103918.740726809</v>
       </c>
       <c r="J2" t="n">
-        <v>1958068.581744205</v>
+        <v>1917158.790728203</v>
       </c>
     </row>
     <row r="3">
@@ -516,31 +516,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148005237.0566424</v>
+        <v>-145165973.5346938</v>
       </c>
       <c r="C3" t="n">
-        <v>893465499.2868516</v>
+        <v>874616429.1143793</v>
       </c>
       <c r="D3" t="n">
-        <v>-111344024.7872749</v>
+        <v>-109515064.8257958</v>
       </c>
       <c r="E3" t="n">
-        <v>16605025.97891812</v>
+        <v>16373573.1130962</v>
       </c>
       <c r="F3" t="n">
-        <v>6636531.792174394</v>
+        <v>6564220.770943819</v>
       </c>
       <c r="G3" t="n">
-        <v>-4472591.681449256</v>
+        <v>-4379134.620056569</v>
       </c>
       <c r="H3" t="n">
-        <v>8965870.945704388</v>
+        <v>8787523.95734537</v>
       </c>
       <c r="I3" t="n">
-        <v>-27617039.3796506</v>
+        <v>-27087104.14978569</v>
       </c>
       <c r="J3" t="n">
-        <v>-7452963.89540746</v>
+        <v>-7309586.231574745</v>
       </c>
     </row>
     <row r="4">
@@ -550,31 +550,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46500797.20749153</v>
+        <v>45581849.69682179</v>
       </c>
       <c r="C4" t="n">
-        <v>-111344024.7763549</v>
+        <v>-109515064.8435085</v>
       </c>
       <c r="D4" t="n">
-        <v>54893365.23520559</v>
+        <v>53733421.12671513</v>
       </c>
       <c r="E4" t="n">
-        <v>793229.8339020922</v>
+        <v>774714.2569362768</v>
       </c>
       <c r="F4" t="n">
-        <v>-913245.4730555015</v>
+        <v>-909309.7923643766</v>
       </c>
       <c r="G4" t="n">
-        <v>1157336.032151716</v>
+        <v>1128797.330294316</v>
       </c>
       <c r="H4" t="n">
-        <v>-3234671.32902831</v>
+        <v>-3167222.696963212</v>
       </c>
       <c r="I4" t="n">
-        <v>7559822.774260156</v>
+        <v>7399681.57557621</v>
       </c>
       <c r="J4" t="n">
-        <v>2043262.529416209</v>
+        <v>1999871.451400138</v>
       </c>
     </row>
     <row r="5">
@@ -584,31 +584,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-588057.4181561287</v>
+        <v>-580802.6105220579</v>
       </c>
       <c r="C5" t="n">
-        <v>16605025.97989361</v>
+        <v>16373573.11167445</v>
       </c>
       <c r="D5" t="n">
-        <v>793229.8335153393</v>
+        <v>774714.2575002883</v>
       </c>
       <c r="E5" t="n">
-        <v>1022606.011761798</v>
+        <v>1014723.833202891</v>
       </c>
       <c r="F5" t="n">
-        <v>63279.24836812064</v>
+        <v>63199.67088806778</v>
       </c>
       <c r="G5" t="n">
-        <v>-75772.40204461841</v>
+        <v>-75223.71850405975</v>
       </c>
       <c r="H5" t="n">
-        <v>-2041.389946148849</v>
+        <v>-1917.507072512332</v>
       </c>
       <c r="I5" t="n">
-        <v>-295595.2829141963</v>
+        <v>-293174.2485529436</v>
       </c>
       <c r="J5" t="n">
-        <v>-79834.20817330413</v>
+        <v>-79186.01755954034</v>
       </c>
     </row>
     <row r="6">
@@ -618,31 +618,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1348920.817667929</v>
+        <v>-1341304.423967512</v>
       </c>
       <c r="C6" t="n">
-        <v>6636531.792355914</v>
+        <v>6564220.770669843</v>
       </c>
       <c r="D6" t="n">
-        <v>-913245.4730797858</v>
+        <v>-909309.7921876955</v>
       </c>
       <c r="E6" t="n">
-        <v>63279.24837192587</v>
+        <v>63199.67089327604</v>
       </c>
       <c r="F6" t="n">
-        <v>582396.8324677978</v>
+        <v>578240.9376346583</v>
       </c>
       <c r="G6" t="n">
-        <v>99925.90871882709</v>
+        <v>99794.77834507539</v>
       </c>
       <c r="H6" t="n">
-        <v>40774.07318896861</v>
+        <v>40391.60606532779</v>
       </c>
       <c r="I6" t="n">
-        <v>-14735.8937587831</v>
+        <v>-13686.18883704374</v>
       </c>
       <c r="J6" t="n">
-        <v>-2293.512771024609</v>
+        <v>-2002.347219474238</v>
       </c>
     </row>
     <row r="7">
@@ -652,31 +652,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1066599.767014834</v>
+        <v>1039709.187964997</v>
       </c>
       <c r="C7" t="n">
-        <v>-4472591.681269914</v>
+        <v>-4379134.620355741</v>
       </c>
       <c r="D7" t="n">
-        <v>1157336.032215955</v>
+        <v>1128797.330236208</v>
       </c>
       <c r="E7" t="n">
-        <v>-75772.40203283144</v>
+        <v>-75223.71851843558</v>
       </c>
       <c r="F7" t="n">
-        <v>99925.90872018988</v>
+        <v>99794.77834117236</v>
       </c>
       <c r="G7" t="n">
-        <v>71677.9097425751</v>
+        <v>70770.48036209344</v>
       </c>
       <c r="H7" t="n">
-        <v>-82724.82226459144</v>
+        <v>-80840.12956229516</v>
       </c>
       <c r="I7" t="n">
-        <v>259398.9110597585</v>
+        <v>254523.7075013757</v>
       </c>
       <c r="J7" t="n">
-        <v>70873.40035314878</v>
+        <v>69553.96325485784</v>
       </c>
     </row>
     <row r="8">
@@ -686,31 +686,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2930517.236132021</v>
+        <v>-2870677.14674305</v>
       </c>
       <c r="C8" t="n">
-        <v>8965870.945115587</v>
+        <v>8787523.95827708</v>
       </c>
       <c r="D8" t="n">
-        <v>-3234671.32906802</v>
+        <v>-3167222.696906952</v>
       </c>
       <c r="E8" t="n">
-        <v>-2041.38997022906</v>
+        <v>-1917.507037621954</v>
       </c>
       <c r="F8" t="n">
-        <v>40774.07318700408</v>
+        <v>40391.60607559001</v>
       </c>
       <c r="G8" t="n">
-        <v>-82724.82226181155</v>
+        <v>-80840.12956442063</v>
       </c>
       <c r="H8" t="n">
-        <v>202682.2811658795</v>
+        <v>198405.2064881964</v>
       </c>
       <c r="I8" t="n">
-        <v>-499249.1349861964</v>
+        <v>-488685.8627817878</v>
       </c>
       <c r="J8" t="n">
-        <v>-134984.6682923818</v>
+        <v>-132123.535112764</v>
       </c>
     </row>
     <row r="9">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7254977.249111942</v>
+        <v>7103918.74063317</v>
       </c>
       <c r="C9" t="n">
-        <v>-27617039.37853128</v>
+        <v>-27087104.15160418</v>
       </c>
       <c r="D9" t="n">
-        <v>7559822.774511473</v>
+        <v>7399681.575241826</v>
       </c>
       <c r="E9" t="n">
-        <v>-295595.2828532541</v>
+        <v>-293174.2486381761</v>
       </c>
       <c r="F9" t="n">
-        <v>-14735.89375235676</v>
+        <v>-13686.18886044084</v>
       </c>
       <c r="G9" t="n">
-        <v>259398.9110573159</v>
+        <v>254523.7075016885</v>
       </c>
       <c r="H9" t="n">
-        <v>-499249.1349955797</v>
+        <v>-488685.8627699066</v>
       </c>
       <c r="I9" t="n">
-        <v>1360674.733508436</v>
+        <v>1333588.201508882</v>
       </c>
       <c r="J9" t="n">
-        <v>368633.3830704075</v>
+        <v>361299.2223896576</v>
       </c>
     </row>
     <row r="10">
@@ -754,31 +754,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1958068.581770845</v>
+        <v>1917158.790703002</v>
       </c>
       <c r="C10" t="n">
-        <v>-7452963.895106772</v>
+        <v>-7309586.232063808</v>
       </c>
       <c r="D10" t="n">
-        <v>2043262.529484396</v>
+        <v>1999871.451310307</v>
       </c>
       <c r="E10" t="n">
-        <v>-79834.20815671573</v>
+        <v>-79186.01758267994</v>
       </c>
       <c r="F10" t="n">
-        <v>-2293.512769282442</v>
+        <v>-2002.347225802248</v>
       </c>
       <c r="G10" t="n">
-        <v>70873.40035249558</v>
+        <v>69553.96325494666</v>
       </c>
       <c r="H10" t="n">
-        <v>-134984.6682949461</v>
+        <v>-132123.5351095611</v>
       </c>
       <c r="I10" t="n">
-        <v>368633.3830704574</v>
+        <v>361299.2223896818</v>
       </c>
       <c r="J10" t="n">
-        <v>99937.28304164347</v>
+        <v>97951.40732676418</v>
       </c>
     </row>
   </sheetData>
